--- a/data/raw/biosphere3_mapping.xlsx
+++ b/data/raw/biosphere3_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI_copy/other_versions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D58D9A-C9F1-0E41-9B40-E40DCFDF7E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52C34EF-9842-CF45-A2BE-06A6828768C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3880" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5208,7 +5208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5235,12 +5235,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri (Textkörper)"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -26456,6 +26450,9 @@
       </c>
     </row>
     <row r="1490" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1490" s="1">
+        <v>1510</v>
+      </c>
       <c r="B1490" t="s">
         <v>1701</v>
       </c>
@@ -26467,6 +26464,9 @@
       </c>
     </row>
     <row r="1491" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1491" s="1">
+        <v>1511</v>
+      </c>
       <c r="B1491" t="s">
         <v>1702</v>
       </c>
